--- a/data/trans_orig/P05A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>605058</t>
+          <t>604772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>636516</t>
+          <t>637779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>607451</t>
+          <t>606882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>637281</t>
+          <t>637828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1221051</t>
+          <t>1225158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1267703</t>
+          <t>1270629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80078</t>
+          <t>81221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70031</t>
+          <t>68694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98654</t>
+          <t>96830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>138734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25561</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>808167</t>
+          <t>806076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>850576</t>
+          <t>849247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>806795</t>
+          <t>807188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>852155</t>
+          <t>853186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1631553</t>
+          <t>1632145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1692693</t>
+          <t>1693263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88233</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127886</t>
+          <t>131450</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90259</t>
+          <t>88351</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131082</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187085</t>
+          <t>185843</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242700</t>
+          <t>244163</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59176</t>
+          <t>61100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498282</t>
+          <t>497105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>543869</t>
+          <t>542749</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>525781</t>
+          <t>524880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>567731</t>
+          <t>567412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1036142</t>
+          <t>1037691</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1098060</t>
+          <t>1096533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112072</t>
+          <t>114748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154812</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>91649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130624</t>
+          <t>131114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216219</t>
+          <t>217058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273285</t>
+          <t>273898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>31498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>33258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>29926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>686399</t>
+          <t>684634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>738019</t>
+          <t>734929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>724260</t>
+          <t>725260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>780984</t>
+          <t>782547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1427844</t>
+          <t>1423577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1504035</t>
+          <t>1500582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147927</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193840</t>
+          <t>195222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206077</t>
+          <t>207283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260207</t>
+          <t>263042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369372</t>
+          <t>369668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439112</t>
+          <t>440802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59029</t>
+          <t>58340</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30296</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55097</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>69299</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105733</t>
+          <t>105335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2642423</t>
+          <t>2646875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2726713</t>
+          <t>2730191</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2707237</t>
+          <t>2709781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2801468</t>
+          <t>2799803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5378735</t>
+          <t>5381129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5504669</t>
+          <t>5509040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>436667</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>515588</t>
+          <t>513509</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>466910</t>
+          <t>466603</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>553420</t>
+          <t>550222</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>926341</t>
+          <t>917937</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1042746</t>
+          <t>1033918</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109152</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>165470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>216873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>673723</t>
+          <t>672747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>689240</t>
+          <t>689633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>646773</t>
+          <t>646572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>671211</t>
+          <t>670889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1325965</t>
+          <t>1326090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1355327</t>
+          <t>1356387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>39147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>29924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>57951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>870379</t>
+          <t>867461</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>913048</t>
+          <t>912862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>883494</t>
+          <t>883067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>926360</t>
+          <t>925764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1769975</t>
+          <t>1766797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1827972</t>
+          <t>1826226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75642</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112188</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114588</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161402</t>
+          <t>162720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>214423</t>
+          <t>217422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>630385</t>
+          <t>631105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>671161</t>
+          <t>670470</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>664977</t>
+          <t>665832</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>702390</t>
+          <t>702246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1311507</t>
+          <t>1310539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1367268</t>
+          <t>1365692</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71057</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>111335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>66532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102250</t>
+          <t>102714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146074</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>199521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28468</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>726602</t>
+          <t>726258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>774987</t>
+          <t>776493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>790603</t>
+          <t>790746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>842986</t>
+          <t>842945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1533552</t>
+          <t>1531029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1608700</t>
+          <t>1604677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120555</t>
+          <t>119422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164036</t>
+          <t>164206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140811</t>
+          <t>140826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188475</t>
+          <t>189272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270643</t>
+          <t>270750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337210</t>
+          <t>338377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>29478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56477</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58097</t>
+          <t>57855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104512</t>
+          <t>104668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2938863</t>
+          <t>2937924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3021739</t>
+          <t>3019012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3027798</t>
+          <t>3032703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3110370</t>
+          <t>3111893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5988779</t>
+          <t>5994458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6101308</t>
+          <t>6105418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>304976</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>377476</t>
+          <t>376430</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>329938</t>
+          <t>325693</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>405077</t>
+          <t>400681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>655334</t>
+          <t>659790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>758307</t>
+          <t>763388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100482</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94623</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129674</t>
+          <t>128063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>619386</t>
+          <t>617967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>642786</t>
+          <t>642353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>619567</t>
+          <t>618832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>642757</t>
+          <t>641504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1247028</t>
+          <t>1246802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1280625</t>
+          <t>1280724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48104</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>48462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81934</t>
+          <t>80959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>880646</t>
+          <t>882017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>921807</t>
+          <t>922500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>882000</t>
+          <t>881483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925477</t>
+          <t>924279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1777577</t>
+          <t>1772949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1838084</t>
+          <t>1834416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>58215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>92786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70906</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107243</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139347</t>
+          <t>141934</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190471</t>
+          <t>190418</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56950</t>
+          <t>58416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66770</t>
+          <t>68223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106072</t>
+          <t>106880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>545697</t>
+          <t>549514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597045</t>
+          <t>597501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>559432</t>
+          <t>563062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>609003</t>
+          <t>609484</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1126148</t>
+          <t>1128307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1194094</t>
+          <t>1194952</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>117392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163419</t>
+          <t>163987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121987</t>
+          <t>120431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167040</t>
+          <t>164621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246572</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311315</t>
+          <t>311232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59005</t>
+          <t>57585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>66755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77570</t>
+          <t>77317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115889</t>
+          <t>115564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>720417</t>
+          <t>717818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>769184</t>
+          <t>765592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>789260</t>
+          <t>789121</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>842942</t>
+          <t>843023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1529724</t>
+          <t>1527423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1601203</t>
+          <t>1600450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135336</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180231</t>
+          <t>183186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155750</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205316</t>
+          <t>203278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300425</t>
+          <t>296274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368524</t>
+          <t>366307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50096</t>
+          <t>50694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44054</t>
+          <t>44708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77215</t>
+          <t>77684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2810143</t>
+          <t>2806456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2894074</t>
+          <t>2893237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2899210</t>
+          <t>2894161</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2989091</t>
+          <t>2986248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5731159</t>
+          <t>5726231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5856322</t>
+          <t>5849735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368315</t>
+          <t>367523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>441768</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>393223</t>
+          <t>394783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>473483</t>
+          <t>480150</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>783832</t>
+          <t>785637</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>895715</t>
+          <t>900310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90057</t>
+          <t>90441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133003</t>
+          <t>131766</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113129</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213614</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>278476</t>
+          <t>280469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607424</t>
+          <t>607073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>623685</t>
+          <t>623645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>691728</t>
+          <t>690945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>708910</t>
+          <t>709299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,47 +8319,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1319087</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1305029</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1329542</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>97,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1319087</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1306402</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1329900</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1101272</t>
+          <t>1099201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1158885</t>
+          <t>1157523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>868021</t>
+          <t>866418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>895581</t>
+          <t>895515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1980312</t>
+          <t>1979834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2050761</t>
+          <t>2050923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56882</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61475</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109884</t>
+          <t>110432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>612030</t>
+          <t>611805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646546</t>
+          <t>645843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>839297</t>
+          <t>840073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>895474</t>
+          <t>895879</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1463803</t>
+          <t>1466651</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1542310</t>
+          <t>1546072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82833</t>
+          <t>83905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78090</t>
+          <t>78143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77983</t>
+          <t>74813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151218</t>
+          <t>147672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,47 +9457,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>11810</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>5828</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>19984</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>11810</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6359</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>19594</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>755633</t>
+          <t>756759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>806460</t>
+          <t>803521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>883901</t>
+          <t>880455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>942756</t>
+          <t>940158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1652039</t>
+          <t>1658505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1731322</t>
+          <t>1734372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84445</t>
+          <t>85950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128162</t>
+          <t>128105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108813</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157875</t>
+          <t>159555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207669</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272890</t>
+          <t>270004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49378</t>
+          <t>48810</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>93647</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3111175</t>
+          <t>3114691</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3221765</t>
+          <t>3219126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3312526</t>
+          <t>3314224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3415724</t>
+          <t>3415645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6452452</t>
+          <t>6452127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6599474</t>
+          <t>6597699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>175934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>259191</t>
+          <t>259850</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>214492</t>
+          <t>214691</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>297319</t>
+          <t>295560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>416420</t>
+          <t>414946</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>531429</t>
+          <t>533341</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88858</t>
+          <t>88356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>57999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>94586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111445</t>
+          <t>114284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167690</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>604772</t>
+          <t>605077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>637779</t>
+          <t>638066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>606882</t>
+          <t>607610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>637828</t>
+          <t>638586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1225158</t>
+          <t>1222440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1270629</t>
+          <t>1266877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>49272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81221</t>
+          <t>80210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>41436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68694</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96830</t>
+          <t>98221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138734</t>
+          <t>139433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>806076</t>
+          <t>806092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>849247</t>
+          <t>849119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>807188</t>
+          <t>808365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>853186</t>
+          <t>853694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1632145</t>
+          <t>1631190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1693263</t>
+          <t>1693156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88971</t>
+          <t>88488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131450</t>
+          <t>128445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88351</t>
+          <t>88340</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129667</t>
+          <t>130992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>185843</t>
+          <t>187294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>244163</t>
+          <t>243331</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>24772</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>36882</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>43130</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>57697</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>3,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>24772</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15488</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35341</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>43130</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>32118</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>61100</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497105</t>
+          <t>498963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>542749</t>
+          <t>543333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>524880</t>
+          <t>525222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>567412</t>
+          <t>566125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1037691</t>
+          <t>1037902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1096533</t>
+          <t>1098682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114748</t>
+          <t>112580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>155546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91649</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131114</t>
+          <t>130587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217058</t>
+          <t>216239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273898</t>
+          <t>274688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31498</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57419</t>
+          <t>57872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>684634</t>
+          <t>686256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>734929</t>
+          <t>735617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>725260</t>
+          <t>724098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>782547</t>
+          <t>780744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1423577</t>
+          <t>1423272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1500582</t>
+          <t>1500223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148439</t>
+          <t>147688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195222</t>
+          <t>193761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207283</t>
+          <t>209562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263042</t>
+          <t>260990</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369668</t>
+          <t>369591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>440802</t>
+          <t>443476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>33920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58340</t>
+          <t>59489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,47 +2377,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>86372</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>69760</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>105742</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>5,41%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>86372</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>69299</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>105335</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2646875</t>
+          <t>2639528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2730191</t>
+          <t>2724742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2709781</t>
+          <t>2711913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2799803</t>
+          <t>2804819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5381129</t>
+          <t>5379320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5509040</t>
+          <t>5502081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>436005</t>
+          <t>437144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>513509</t>
+          <t>518706</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>466603</t>
+          <t>463855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>550222</t>
+          <t>549148</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>917937</t>
+          <t>930705</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1033918</t>
+          <t>1042153</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71632</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110735</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>119162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165470</t>
+          <t>161586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216873</t>
+          <t>216013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>672747</t>
+          <t>669930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>689633</t>
+          <t>688973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>646572</t>
+          <t>645020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>670889</t>
+          <t>671351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1326090</t>
+          <t>1324429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1356387</t>
+          <t>1355573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39147</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29924</t>
+          <t>31675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57951</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>867461</t>
+          <t>870785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>912862</t>
+          <t>914472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>883067</t>
+          <t>882925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925764</t>
+          <t>926386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1766797</t>
+          <t>1768026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1826226</t>
+          <t>1827259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>76184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115965</t>
+          <t>114097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>75972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115249</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162720</t>
+          <t>162186</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>217422</t>
+          <t>218382</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34022</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631105</t>
+          <t>629736</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>670470</t>
+          <t>671454</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>665832</t>
+          <t>666356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>702246</t>
+          <t>701244</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1310539</t>
+          <t>1312525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1365692</t>
+          <t>1365385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72025</t>
+          <t>72609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111335</t>
+          <t>109363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66532</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102714</t>
+          <t>102526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145508</t>
+          <t>144447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199521</t>
+          <t>197249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>726258</t>
+          <t>727913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>776493</t>
+          <t>776103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>790746</t>
+          <t>790932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>842945</t>
+          <t>844741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1531029</t>
+          <t>1528560</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1604677</t>
+          <t>1604479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119422</t>
+          <t>120752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164206</t>
+          <t>164918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140826</t>
+          <t>139854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189272</t>
+          <t>188303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270750</t>
+          <t>272781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338377</t>
+          <t>343085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>55441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>66625</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104668</t>
+          <t>104404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2937924</t>
+          <t>2941605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3019012</t>
+          <t>3020455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3032703</t>
+          <t>3027252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3111893</t>
+          <t>3107761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5994458</t>
+          <t>5991280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6105418</t>
+          <t>6105060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>302649</t>
+          <t>303839</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>376430</t>
+          <t>377097</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>325693</t>
+          <t>332649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>400681</t>
+          <t>403887</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>659790</t>
+          <t>656914</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>763388</t>
+          <t>766019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94859</t>
+          <t>93258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>130060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180409</t>
+          <t>182888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>617967</t>
+          <t>619755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>642353</t>
+          <t>643073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>618832</t>
+          <t>618744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>641504</t>
+          <t>642412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1246802</t>
+          <t>1247228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1280724</t>
+          <t>1280028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>40628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80959</t>
+          <t>81216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>882017</t>
+          <t>882097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>922500</t>
+          <t>924639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>881483</t>
+          <t>882510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924279</t>
+          <t>925474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1772949</t>
+          <t>1775936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1834416</t>
+          <t>1835777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58215</t>
+          <t>58048</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92786</t>
+          <t>92699</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>72392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107897</t>
+          <t>107058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141934</t>
+          <t>139896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190418</t>
+          <t>187586</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58416</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57231</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68223</t>
+          <t>66719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106880</t>
+          <t>107027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>549514</t>
+          <t>548793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597501</t>
+          <t>596403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>563062</t>
+          <t>563710</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>609484</t>
+          <t>613341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128307</t>
+          <t>1126145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1194952</t>
+          <t>1196793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117392</t>
+          <t>116434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163987</t>
+          <t>160187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120431</t>
+          <t>122090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164621</t>
+          <t>163544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>248256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311232</t>
+          <t>312482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66755</t>
+          <t>65845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77317</t>
+          <t>76853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115564</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>717818</t>
+          <t>718983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>765592</t>
+          <t>769144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>789121</t>
+          <t>791986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>843023</t>
+          <t>846358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1527423</t>
+          <t>1523848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1600450</t>
+          <t>1598000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136262</t>
+          <t>133602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183186</t>
+          <t>181492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153097</t>
+          <t>153469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203278</t>
+          <t>203588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296274</t>
+          <t>300441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366307</t>
+          <t>368965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50694</t>
+          <t>50781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>44623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77684</t>
+          <t>76590</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2806456</t>
+          <t>2812514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2893237</t>
+          <t>2894719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2894161</t>
+          <t>2897928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2986248</t>
+          <t>2989431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5726231</t>
+          <t>5729540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5849735</t>
+          <t>5856991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367523</t>
+          <t>367860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>441768</t>
+          <t>443425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>394783</t>
+          <t>393553</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>480150</t>
+          <t>474246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>785637</t>
+          <t>788685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>900310</t>
+          <t>901700</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90441</t>
+          <t>89691</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131766</t>
+          <t>131415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115479</t>
+          <t>115967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164123</t>
+          <t>161495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215007</t>
+          <t>211260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280469</t>
+          <t>278521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -8264,17 +8264,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>617285</t>
+          <t>671010</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607073</t>
+          <t>660527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>623645</t>
+          <t>677765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>701802</t>
+          <t>707803</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>690945</t>
+          <t>695895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>709299</t>
+          <t>715800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1319087</t>
+          <t>1378812</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1305029</t>
+          <t>1364967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1329542</t>
+          <t>1390007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44754</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8490,67 +8490,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8189</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>724664</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359086</t>
+          <t>1423103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1125243</t>
+          <t>970499</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1099201</t>
+          <t>948564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1157523</t>
+          <t>987150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>883079</t>
+          <t>986035</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866418</t>
+          <t>968241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>895515</t>
+          <t>1000940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2008322</t>
+          <t>1956535</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1979834</t>
+          <t>1930222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2050923</t>
+          <t>1979690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>55731</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58484</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>125772</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>43281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>24783</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>53255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>38934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64517</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1189964</t>
+          <t>1046097</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1189964</t>
+          <t>1046097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1189964</t>
+          <t>1046097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>954103</t>
+          <t>1066550</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>954103</t>
+          <t>1066550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>954103</t>
+          <t>1066550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2144067</t>
+          <t>2112647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2144067</t>
+          <t>2112647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2144067</t>
+          <t>2112647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631086</t>
+          <t>712053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>611805</t>
+          <t>692320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645843</t>
+          <t>729898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>864531</t>
+          <t>727747</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>840073</t>
+          <t>710547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>895879</t>
+          <t>743033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1495617</t>
+          <t>1439800</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1466651</t>
+          <t>1415173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1546072</t>
+          <t>1462438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65076</t>
+          <t>80141</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83905</t>
+          <t>99638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55355</t>
+          <t>65632</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78143</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>120432</t>
+          <t>145773</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74813</t>
+          <t>124119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147672</t>
+          <t>170735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699542</t>
+          <t>796814</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>699542</t>
+          <t>796814</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>699542</t>
+          <t>796814</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>928317</t>
+          <t>802834</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>928317</t>
+          <t>802834</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>928317</t>
+          <t>802834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1627859</t>
+          <t>1599648</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1627859</t>
+          <t>1599648</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1627859</t>
+          <t>1599648</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>783527</t>
+          <t>841616</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>756759</t>
+          <t>814126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>803521</t>
+          <t>863926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>908554</t>
+          <t>916221</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>880455</t>
+          <t>892844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>940158</t>
+          <t>939004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1692080</t>
+          <t>1757836</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1658505</t>
+          <t>1726050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1734372</t>
+          <t>1790441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104331</t>
+          <t>109273</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85950</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128105</t>
+          <t>134610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135283</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108399</t>
+          <t>125169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159555</t>
+          <t>168097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>239614</t>
+          <t>255446</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203813</t>
+          <t>226989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270004</t>
+          <t>284873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48810</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>70902</t>
+          <t>73908</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93647</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>919222</t>
+          <t>981948</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>919222</t>
+          <t>981948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>919222</t>
+          <t>981948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1083375</t>
+          <t>1105242</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1083375</t>
+          <t>1105242</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1083375</t>
+          <t>1105242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2002596</t>
+          <t>2087189</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2002596</t>
+          <t>2087189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2002596</t>
+          <t>2087189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3157141</t>
+          <t>3195178</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3114691</t>
+          <t>3151438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3219126</t>
+          <t>3229038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3357966</t>
+          <t>3337805</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3314224</t>
+          <t>3303422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3415645</t>
+          <t>3371636</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6515106</t>
+          <t>6532984</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6452127</t>
+          <t>6477671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6597699</t>
+          <t>6580741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>221278</t>
+          <t>250664</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>175934</t>
+          <t>221249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>259850</t>
+          <t>288881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>258962</t>
+          <t>289059</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>214691</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>295560</t>
+          <t>320087</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>480240</t>
+          <t>539722</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>414946</t>
+          <t>497686</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533341</t>
+          <t>590035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64730</t>
+          <t>68641</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88356</t>
+          <t>93302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>73532</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94586</t>
+          <t>99838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>138262</t>
+          <t>149883</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114284</t>
+          <t>128358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>177613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
